--- a/90211_REPORT_BOTTEGA_09-01-2026.xlsx
+++ b/90211_REPORT_BOTTEGA_09-01-2026.xlsx
@@ -9,13 +9,12 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
-    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="60">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -50,39 +49,6 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
-    <t>16:00 - 16:59</t>
-  </si>
-  <si>
-    <t>17:00 - 17:59</t>
-  </si>
-  <si>
-    <t>18:00 - 18:59</t>
-  </si>
-  <si>
-    <t>19:00 - 19:59</t>
-  </si>
-  <si>
-    <t>20:00 - 20:59</t>
-  </si>
-  <si>
-    <t>21:00 - 21:59</t>
-  </si>
-  <si>
-    <t>22:00 - 22:59</t>
-  </si>
-  <si>
-    <t>23:00 - 23:59</t>
-  </si>
-  <si>
-    <t>0:00 - 0:59</t>
-  </si>
-  <si>
-    <t>1:00 - 1:59</t>
-  </si>
-  <si>
-    <t>2:00 - 2:59</t>
-  </si>
-  <si>
     <t>TOTALE INCASSI 09/01/2026</t>
   </si>
   <si>
@@ -119,28 +85,52 @@
     <t>Tagliata di pollo</t>
   </si>
   <si>
+    <t>50-004-010-000650</t>
+  </si>
+  <si>
+    <t>Pollo al curry</t>
+  </si>
+  <si>
+    <t>50-004-010-000010</t>
+  </si>
+  <si>
+    <t>Gran piatto per 2</t>
+  </si>
+  <si>
+    <t>50-004-010-000610</t>
+  </si>
+  <si>
+    <t>Riso con verdure</t>
+  </si>
+  <si>
     <t>50-004-010-000110</t>
   </si>
   <si>
     <t>Pollo alla cacciatora + contorno</t>
   </si>
   <si>
-    <t>50-004-010-000650</t>
-  </si>
-  <si>
-    <t>Pollo al curry</t>
-  </si>
-  <si>
     <t>50-004-010-000100</t>
   </si>
   <si>
     <t>Cosce di pollo</t>
   </si>
   <si>
-    <t>50-004-010-000610</t>
-  </si>
-  <si>
-    <t>Riso con verdure</t>
+    <t>50-004-010-000220</t>
+  </si>
+  <si>
+    <t>Riso</t>
+  </si>
+  <si>
+    <t>50-004-010-000570</t>
+  </si>
+  <si>
+    <t>Verdure miste</t>
+  </si>
+  <si>
+    <t>50-004-010-000330</t>
+  </si>
+  <si>
+    <t>Patate speciali</t>
   </si>
   <si>
     <t>50-004-010-000060</t>
@@ -155,16 +145,16 @@
     <t>Mezzo pollo</t>
   </si>
   <si>
-    <t>50-004-010-000010</t>
-  </si>
-  <si>
-    <t>Gran piatto per 2</t>
-  </si>
-  <si>
-    <t>50-004-010-000330</t>
-  </si>
-  <si>
-    <t>Patate speciali</t>
+    <t>50-004-010-000160</t>
+  </si>
+  <si>
+    <t>Patate</t>
+  </si>
+  <si>
+    <t>50-004-010-000120</t>
+  </si>
+  <si>
+    <t>Caesar salad</t>
   </si>
   <si>
     <t>50-004-010-000320</t>
@@ -173,54 +163,18 @@
     <t>Alette di pollo</t>
   </si>
   <si>
-    <t>50-004-010-000120</t>
-  </si>
-  <si>
-    <t>Caesar salad</t>
-  </si>
-  <si>
-    <t>50-004-010-000220</t>
-  </si>
-  <si>
-    <t>Riso</t>
-  </si>
-  <si>
-    <t>50-004-010-000570</t>
-  </si>
-  <si>
-    <t>Verdure miste</t>
-  </si>
-  <si>
-    <t>50-004-010-000160</t>
-  </si>
-  <si>
-    <t>Patate</t>
-  </si>
-  <si>
     <t>50-004-010-000590</t>
   </si>
   <si>
     <t>Salsa</t>
   </si>
   <si>
-    <t>50-004-010-000600</t>
-  </si>
-  <si>
-    <t>Verza</t>
-  </si>
-  <si>
     <t>50-004-010-000170</t>
   </si>
   <si>
     <t>Insalata mista</t>
   </si>
   <si>
-    <t>50-004-010-000640</t>
-  </si>
-  <si>
-    <t>Aggiunta Contorno</t>
-  </si>
-  <si>
     <t>50-004-010-888888</t>
   </si>
   <si>
@@ -240,21 +194,6 @@
   </si>
   <si>
     <t>12:00-15:59</t>
-  </si>
-  <si>
-    <t>16:00-18:59</t>
-  </si>
-  <si>
-    <t>19:00-02:59</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>VAR %</t>
-  </si>
-  <si>
-    <t>10/01/2025</t>
   </si>
 </sst>
 </file>
@@ -392,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -405,27 +344,13 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -513,115 +438,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
+      <c r="A11" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="5">
-        <v>0.0</v>
+      <c r="B11" t="n" s="1">
+        <v>991.4</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="4">
+      <c r="A12" t="s" s="1">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="7">
-        <v>49.0</v>
+      <c r="B12" t="n" s="1">
+        <v>1192.19</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="2">
+      <c r="A13" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="5">
-        <v>147.893</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n" s="7">
-        <v>149.9094</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n" s="5">
-        <v>168.0553</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="4">
-        <v>16</v>
-      </c>
-      <c r="B16" t="n" s="7">
-        <v>105.9644</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B17" t="n" s="5">
-        <v>75.1818</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="4">
-        <v>18</v>
-      </c>
-      <c r="B18" t="n" s="7">
-        <v>11.8182</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B19" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="B20" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B21" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="1">
-        <v>22</v>
-      </c>
-      <c r="B22" t="n" s="1">
-        <v>1699.22</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>23</v>
-      </c>
-      <c r="B23" t="n" s="1">
-        <v>1766.33</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B24" t="n" s="1">
-        <v>-3.8</v>
+      <c r="B13" t="n" s="1">
+        <v>-16.84</v>
       </c>
     </row>
   </sheetData>
@@ -631,7 +468,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -643,373 +480,339 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>864.3</v>
+        <v>479.6455</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>74.0</v>
+        <v>41.0</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>50.86</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>152.4544</v>
+        <v>140.7271</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>8.97</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>93.8184</v>
+        <v>81.0</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>5.52</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>90.0</v>
+        <v>47.091</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>88.2</v>
+        <v>36.3636</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>5.19</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>54.5455</v>
+        <v>35.1819</v>
       </c>
       <c r="D7" t="n" s="5">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>3.21</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>54.5454</v>
+        <v>27.0</v>
       </c>
       <c r="D8" t="n" s="7">
         <v>3.0</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>3.21</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>53.0909</v>
+        <v>26.8183</v>
       </c>
       <c r="D9" t="n" s="5">
         <v>6.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>3.12</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>47.091</v>
+        <v>22.7273</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>40.9092</v>
+        <v>18.1819</v>
       </c>
       <c r="D11" t="n" s="5">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>2.41</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n" s="7">
-        <v>36.0</v>
+        <v>18.1818</v>
       </c>
       <c r="D12" t="n" s="7">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>35.1818</v>
+        <v>17.0909</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n" s="7">
-        <v>31.3638</v>
+        <v>14.5455</v>
       </c>
       <c r="D14" t="n" s="7">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="E14" t="n" s="7">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>27.2728</v>
+        <v>11.7273</v>
       </c>
       <c r="D15" t="n" s="5">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="E15" t="n" s="5">
-        <v>1.61</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C16" t="n" s="7">
-        <v>14.5455</v>
+        <v>9.0</v>
       </c>
       <c r="D16" t="n" s="7">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="E16" t="n" s="7">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C17" t="n" s="5">
-        <v>5.2727</v>
+        <v>2.8181</v>
       </c>
       <c r="D17" t="n" s="5">
-        <v>58.0</v>
+        <v>31.0</v>
       </c>
       <c r="E17" t="n" s="5">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C18" t="n" s="7">
-        <v>4.5455</v>
+        <v>2.7273</v>
       </c>
       <c r="D18" t="n" s="7">
         <v>1.0</v>
       </c>
       <c r="E18" t="n" s="7">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C19" t="n" s="5">
-        <v>2.7273</v>
+        <v>0.5738</v>
       </c>
       <c r="D19" t="n" s="5">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="E19" t="n" s="5">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>66</v>
-      </c>
-      <c r="B20" t="s" s="4">
-        <v>67</v>
-      </c>
-      <c r="C20" t="n" s="7">
-        <v>1.8182</v>
-      </c>
-      <c r="D20" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="E20" t="n" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="C21" t="n" s="5">
-        <v>1.541</v>
-      </c>
-      <c r="D21" t="n" s="5">
-        <v>19.0</v>
-      </c>
-      <c r="E21" t="n" s="5">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="1">
-        <v>70</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" t="n" s="1">
-        <v>1699.22</v>
-      </c>
-      <c r="D22" t="n" s="1">
-        <v>252.0</v>
-      </c>
-      <c r="E22" t="n" s="1">
+      <c r="A20" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" t="n" s="1">
+        <v>991.4</v>
+      </c>
+      <c r="D20" t="n" s="1">
+        <v>141.0</v>
+      </c>
+      <c r="E20" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -1020,7 +823,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -1031,13 +834,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -1045,15 +848,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>6.0</v>
@@ -1064,10 +867,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>3.0</v>
@@ -1078,10 +881,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>2.0</v>
@@ -1092,10 +895,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>2.0</v>
@@ -1106,10 +909,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C7" t="n" s="5">
         <v>2.0</v>
@@ -1120,10 +923,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n" s="7">
         <v>1.0</v>
@@ -1134,10 +937,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>1.0</v>
@@ -1148,10 +951,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>1.0</v>
@@ -1162,10 +965,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>1.0</v>
@@ -1176,10 +979,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>1.0</v>
@@ -1190,10 +993,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>1.0</v>
@@ -1204,10 +1007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="1">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C14" t="n" s="1">
         <v>21.0</v>
@@ -1219,15 +1022,15 @@
     <row r="15"/>
     <row r="16">
       <c r="A16" t="s" s="1">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>38.0</v>
@@ -1238,10 +1041,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C18" t="n" s="7">
         <v>25.0</v>
@@ -1252,10 +1055,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>10.0</v>
@@ -1266,10 +1069,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C20" t="n" s="7">
         <v>8.0</v>
@@ -1280,10 +1083,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>6.0</v>
@@ -1294,10 +1097,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C22" t="n" s="7">
         <v>6.0</v>
@@ -1308,10 +1111,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C23" t="n" s="5">
         <v>5.0</v>
@@ -1322,10 +1125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n" s="7">
         <v>5.0</v>
@@ -1336,10 +1139,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C25" t="n" s="5">
         <v>4.0</v>
@@ -1350,10 +1153,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C26" t="n" s="7">
         <v>3.0</v>
@@ -1364,10 +1167,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C27" t="n" s="5">
         <v>2.0</v>
@@ -1378,10 +1181,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C28" t="n" s="7">
         <v>2.0</v>
@@ -1392,10 +1195,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C29" t="n" s="5">
         <v>2.0</v>
@@ -1406,10 +1209,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="4">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s" s="4">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C30" t="n" s="7">
         <v>1.0</v>
@@ -1420,10 +1223,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n" s="5">
         <v>1.0</v>
@@ -1434,10 +1237,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="4">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s" s="4">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C32" t="n" s="7">
         <v>1.0</v>
@@ -1448,10 +1251,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C33" t="n" s="5">
         <v>1.0</v>
@@ -1462,10 +1265,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="1">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s" s="4">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C34" t="n" s="1">
         <v>120.0</v>
@@ -1475,431 +1278,13 @@
       </c>
     </row>
     <row r="35"/>
-    <row r="36">
-      <c r="A36" t="s" s="1">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C37" t="n" s="5">
-        <v>11.0</v>
-      </c>
-      <c r="D37" t="n" s="5">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="4">
-        <v>30</v>
-      </c>
-      <c r="B38" t="s" s="4">
-        <v>31</v>
-      </c>
-      <c r="C38" t="n" s="7">
-        <v>9.0</v>
-      </c>
-      <c r="D38" t="n" s="7">
-        <v>105.5454</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C39" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D39" t="n" s="5">
-        <v>23.4546</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="4">
-        <v>52</v>
-      </c>
-      <c r="B40" t="s" s="4">
-        <v>53</v>
-      </c>
-      <c r="C40" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D40" t="n" s="7">
-        <v>23.4545</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="C41" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D41" t="n" s="5">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="4">
-        <v>68</v>
-      </c>
-      <c r="B42" t="s" s="4">
-        <v>69</v>
-      </c>
-      <c r="C42" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D42" t="n" s="7">
-        <v>0.1475</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="C43" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D43" t="n" s="5">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="4">
-        <v>36</v>
-      </c>
-      <c r="B44" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="C44" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D44" t="n" s="7">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="C45" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D45" t="n" s="5">
-        <v>4.5455</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="4">
-        <v>40</v>
-      </c>
-      <c r="B46" t="s" s="4">
-        <v>41</v>
-      </c>
-      <c r="C46" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D46" t="n" s="7">
-        <v>4.5455</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="1">
-        <v>72</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="C47" t="n" s="1">
-        <v>32.0</v>
-      </c>
-      <c r="D47" t="n" s="1">
-        <v>196.89</v>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" t="s" s="1">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="4">
-        <v>30</v>
-      </c>
-      <c r="B50" t="s" s="4">
-        <v>31</v>
-      </c>
-      <c r="C50" t="n" s="7">
-        <v>24.0</v>
-      </c>
-      <c r="D50" t="n" s="7">
-        <v>279.1091</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C51" t="n" s="5">
-        <v>16.0</v>
-      </c>
-      <c r="D51" t="n" s="5">
-        <v>1.4546</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="4">
-        <v>68</v>
-      </c>
-      <c r="B52" t="s" s="4">
-        <v>69</v>
-      </c>
-      <c r="C52" t="n" s="7">
-        <v>10.0</v>
-      </c>
-      <c r="D52" t="n" s="7">
-        <v>0.8197</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="C53" t="n" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="D53" t="n" s="5">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="4">
-        <v>48</v>
-      </c>
-      <c r="B54" t="s" s="4">
-        <v>49</v>
-      </c>
-      <c r="C54" t="n" s="7">
-        <v>5.0</v>
-      </c>
-      <c r="D54" t="n" s="7">
-        <v>22.7273</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="C55" t="n" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="D55" t="n" s="5">
-        <v>36.0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="4">
-        <v>34</v>
-      </c>
-      <c r="B56" t="s" s="4">
-        <v>35</v>
-      </c>
-      <c r="C56" t="n" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="D56" t="n" s="7">
-        <v>35.1819</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="C57" t="n" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="D57" t="n" s="5">
-        <v>13.6364</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="4">
-        <v>42</v>
-      </c>
-      <c r="B58" t="s" s="4">
-        <v>43</v>
-      </c>
-      <c r="C58" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D58" t="n" s="7">
-        <v>36.3636</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="C59" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D59" t="n" s="5">
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="4">
-        <v>66</v>
-      </c>
-      <c r="B60" t="s" s="4">
-        <v>67</v>
-      </c>
-      <c r="C60" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D60" t="n" s="7">
-        <v>1.8182</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="C61" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D61" t="n" s="5">
-        <v>11.7273</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="4">
-        <v>54</v>
-      </c>
-      <c r="B62" t="s" s="4">
-        <v>55</v>
-      </c>
-      <c r="C62" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D62" t="n" s="7">
-        <v>4.5455</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="C63" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D63" t="n" s="5">
-        <v>4.5455</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="1">
-        <v>72</v>
-      </c>
-      <c r="B64" t="s" s="4">
-        <v>73</v>
-      </c>
-      <c r="C64" t="n" s="1">
-        <v>79.0</v>
-      </c>
-      <c r="D64" t="n" s="1">
-        <v>510.93</v>
-      </c>
-    </row>
-    <row r="65"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="4">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A64:B64"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>77</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>78</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n" s="9">
-        <v>6216.0</v>
-      </c>
-      <c r="B2" s="12" t="n">
-        <f>(A2-C2)/C2</f>
-        <v>0.0</v>
-      </c>
-      <c r="C2" t="n" s="9">
-        <v>6820.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>